--- a/Fortran/results/Test_results.xlsx
+++ b/Fortran/results/Test_results.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\proek\Documents\GitHub\ModAB-Root-Finding\Fortran\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CFA98DB-C27C-4598-9CF7-33F6AC78006C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26DB781E-9DC0-49C1-A017-5BB2927719AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{901E7075-F730-4135-A5B3-71A5C4E5AAAF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$Y$236</definedName>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="271">
   <si>
     <t>No.</t>
   </si>
@@ -814,6 +815,48 @@
   <si>
     <t>chandr</t>
   </si>
+  <si>
+    <t>ITP</t>
+  </si>
+  <si>
+    <t>Muller</t>
+  </si>
+  <si>
+    <t>Brent</t>
+  </si>
+  <si>
+    <t>A&amp;B</t>
+  </si>
+  <si>
+    <t>false pos</t>
+  </si>
+  <si>
+    <t>Blendtf</t>
+  </si>
+  <si>
+    <t>Ridders</t>
+  </si>
+  <si>
+    <t>Zhang</t>
+  </si>
+  <si>
+    <t>modAB</t>
+  </si>
+  <si>
+    <t>Brenth</t>
+  </si>
+  <si>
+    <t>Brentq</t>
+  </si>
+  <si>
+    <t>Chandrupatla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Method </t>
+  </si>
+  <si>
+    <t>Factor</t>
+  </si>
 </sst>
 </file>
 
@@ -822,7 +865,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -891,6 +934,14 @@
     <font>
       <b/>
       <sz val="16"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -976,7 +1027,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1027,6 +1078,8 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1071,6 +1124,956 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet2!$A$2:$A$21</c:f>
+              <c:strCache>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>Chandrupatla</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>modAB</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Brenth</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Brentq</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Brent</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>toms748</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Ridders</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>bdqrf</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Zhang</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>ITP</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Muller</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>abkk</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>illinois</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>pegasus</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>Blendtf</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>barycentric</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>bisect</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>A&amp;B</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>rbp</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>false pos</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$B$2:$B$21</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>0.98799699924981255</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.187921980495124</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.2104276069017255</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.2111777944486122</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.3060765191297825</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.3087021755438861</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.3132033008252064</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.4579894973743437</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.4722430607651915</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.6395348837209305</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.9054763690922731</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.9951237809452365</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2.2490622655663914</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2.3713428357089272</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>3.2269317329332332</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>3.7996999249812453</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>5.2393098274568644</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>9.1069017254313582</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>33.460990247561895</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-04CF-4285-AE92-1D2727073FBF}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="65"/>
+        <c:axId val="1164692495"/>
+        <c:axId val="1164695855"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1164692495"/>
+        <c:scaling>
+          <c:orientation val="maxMin"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="bg-BG"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1164695855"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="0"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1164695855"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="10"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="t"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="bg-BG"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1164692495"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+        <c:majorUnit val="1"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="bg-BG"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>536575</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>374650</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E536A7B0-4A43-3D8E-114B-DC8752696B59}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -57559,4 +58562,189 @@
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.55118110236220474" bottom="0" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="22" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B11526C3-4ACD-489D-9F6F-E74A54CA3305}">
+  <dimension ref="A1:B21"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="13.1796875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="25" t="s">
+        <v>269</v>
+      </c>
+      <c r="B1" s="25" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>268</v>
+      </c>
+      <c r="B2" s="24">
+        <v>0.98799699924981255</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>265</v>
+      </c>
+      <c r="B3" s="24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>266</v>
+      </c>
+      <c r="B4" s="24">
+        <v>1.187921980495124</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>267</v>
+      </c>
+      <c r="B5" s="24">
+        <v>1.2104276069017255</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>259</v>
+      </c>
+      <c r="B6" s="24">
+        <v>1.2111777944486122</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="24">
+        <v>1.3060765191297825</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>263</v>
+      </c>
+      <c r="B8" s="24">
+        <v>1.3087021755438861</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="24">
+        <v>1.3132033008252064</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>264</v>
+      </c>
+      <c r="B10" s="24">
+        <v>1.4579894973743437</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>257</v>
+      </c>
+      <c r="B11" s="24">
+        <v>1.4722430607651915</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>258</v>
+      </c>
+      <c r="B12" s="24">
+        <v>1.6395348837209305</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" s="24">
+        <v>1.9054763690922731</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" s="24">
+        <v>1.9951237809452365</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="24">
+        <v>2.2490622655663914</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>262</v>
+      </c>
+      <c r="B16" s="24">
+        <v>2.3713428357089272</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17" s="24">
+        <v>3.2269317329332332</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>206</v>
+      </c>
+      <c r="B18" s="24">
+        <v>3.7996999249812453</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>260</v>
+      </c>
+      <c r="B19" s="24">
+        <v>5.2393098274568644</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" s="24">
+        <v>9.1069017254313582</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>261</v>
+      </c>
+      <c r="B21" s="24">
+        <v>33.460990247561895</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B24">
+    <sortCondition ref="B2:B24"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>